--- a/data/Markspen_Engineering_Central_Monitor.xlsx
+++ b/data/Markspen_Engineering_Central_Monitor.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="675" windowWidth="34200" windowHeight="19785"/>
+    <workbookView xWindow="0" yWindow="675" windowWidth="34200" windowHeight="19785" firstSheet="6" activeTab="14"/>
   </bookViews>
   <sheets>
-    <sheet name="Branches" sheetId="1" r:id="rId1"/>
-    <sheet name="Job Types" sheetId="2" r:id="rId2"/>
-    <sheet name="Expense Categories" sheetId="3" r:id="rId3"/>
-    <sheet name="Status" sheetId="4" r:id="rId4"/>
-    <sheet name="Technicians" sheetId="5" r:id="rId5"/>
-    <sheet name="Managers" sheetId="6" r:id="rId6"/>
-    <sheet name="Vehicle Types" sheetId="7" r:id="rId7"/>
-    <sheet name="Vehicles" sheetId="17" r:id="rId8"/>
-    <sheet name="Spare Parts" sheetId="9" r:id="rId9"/>
-    <sheet name="Jobs" sheetId="10" r:id="rId10"/>
-    <sheet name="Technicians Assigned" sheetId="11" r:id="rId11"/>
-    <sheet name="Technician Visits" sheetId="12" r:id="rId12"/>
-    <sheet name="Spare Parts Used" sheetId="13" r:id="rId13"/>
-    <sheet name="Expenses" sheetId="14" r:id="rId14"/>
-    <sheet name="Job Closing" sheetId="15" r:id="rId15"/>
+    <sheet sheetId="1" name="Branches" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Job Types" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Expense Categories" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Status" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Technicians" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Managers" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Vehicle Types" state="visible" r:id="rId10"/>
+    <sheet sheetId="17" name="Vehicles" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Spare Parts" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Jobs" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Technicians Assigned" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="Technician Visits" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="Spare Parts Used" state="visible" r:id="rId16"/>
+    <sheet sheetId="14" name="Expenses" state="visible" r:id="rId17"/>
+    <sheet sheetId="15" name="Job Closing" state="visible" r:id="rId18"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="835">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1513" uniqueCount="798">
   <si>
     <t>Branch</t>
   </si>
@@ -999,7 +999,7 @@
     <t>[12-10015D-09] MTS AUTO WIRE - M</t>
   </si>
   <si>
-    <t>[13-0100T4-05] MNMS25 Abrasive Rice Whitener　</t>
+    <t xml:space="preserve">[13-0100T4-05] MNMS25 Abrasive Rice Whitener　</t>
   </si>
   <si>
     <t xml:space="preserve"> Output (t/h)：3 5 x 4T 　 　</t>
@@ -2292,90 +2292,27 @@
     <t>2026-MPH-0001</t>
   </si>
   <si>
-    <t>2026/10/24</t>
-  </si>
-  <si>
-    <t>Customer</t>
-  </si>
-  <si>
-    <t>+94765432123</t>
-  </si>
-  <si>
-    <t>Anuradhapura Factory</t>
+    <t>2026/10/25</t>
   </si>
   <si>
     <t>asd</t>
   </si>
   <si>
-    <t>qef</t>
-  </si>
-  <si>
-    <t>ML-123</t>
-  </si>
-  <si>
-    <t>2026/10/31</t>
-  </si>
-  <si>
-    <t>fghj</t>
-  </si>
-  <si>
     <t>2026/10/30</t>
   </si>
   <si>
-    <t>ghjk</t>
-  </si>
-  <si>
     <t>Medium</t>
   </si>
   <si>
-    <t>2026/11/01</t>
-  </si>
-  <si>
-    <t>kjhg</t>
+    <t>2026/11/02</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2026-MPH-0002</t>
-  </si>
-  <si>
-    <t>axca</t>
-  </si>
-  <si>
-    <t>aca</t>
-  </si>
-  <si>
-    <t>casc</t>
-  </si>
-  <si>
-    <t>ca</t>
-  </si>
-  <si>
-    <t>cad</t>
-  </si>
-  <si>
-    <t>2026/10/27</t>
-  </si>
-  <si>
-    <t>2026/10/25</t>
-  </si>
-  <si>
-    <t>2026/10/29</t>
-  </si>
-  <si>
-    <t>adcac</t>
-  </si>
-  <si>
     <t>Lead Technician</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>Visit Id</t>
   </si>
   <si>
@@ -2403,30 +2340,6 @@
     <t>Updated Date</t>
   </si>
   <si>
-    <t>VIS-1270</t>
-  </si>
-  <si>
-    <t>2026/10/24 08:30</t>
-  </si>
-  <si>
-    <t>08:30</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>VIS-2154</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>VISIT-02155</t>
-  </si>
-  <si>
-    <t>09:30</t>
-  </si>
-  <si>
     <t xml:space="preserve">Unit Price </t>
   </si>
   <si>
@@ -2481,18 +2394,6 @@
     <t>Payment Status</t>
   </si>
   <si>
-    <t>EXP-2026-001</t>
-  </si>
-  <si>
-    <t>Ceypetco</t>
-  </si>
-  <si>
-    <t>edfg</t>
-  </si>
-  <si>
-    <t>Not Paid</t>
-  </si>
-  <si>
     <t>Completion Date</t>
   </si>
   <si>
@@ -2521,18 +2422,6 @@
   </si>
   <si>
     <t>Remarks</t>
-  </si>
-  <si>
-    <t>dfghj</t>
-  </si>
-  <si>
-    <t>ghjmnb</t>
-  </si>
-  <si>
-    <t>gfds</t>
-  </si>
-  <si>
-    <t>gfd</t>
   </si>
 </sst>
 </file>
@@ -2541,41 +2430,41 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="5">
@@ -2953,7 +2842,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="8.85546875"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
   </cols>
@@ -3000,14 +2889,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y3"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Y2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="8.85546875"/>
   <cols>
     <col min="1" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="25" customWidth="1"/>
@@ -3121,46 +3010,46 @@
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
         <v>755</v>
       </c>
       <c r="F2" t="s">
+        <v>755</v>
+      </c>
+      <c r="G2" t="s">
+        <v>755</v>
+      </c>
+      <c r="H2" t="s">
+        <v>755</v>
+      </c>
+      <c r="I2" t="s">
+        <v>755</v>
+      </c>
+      <c r="J2" t="s">
+        <v>755</v>
+      </c>
+      <c r="K2" t="s">
         <v>756</v>
       </c>
-      <c r="G2" t="s">
+      <c r="L2" t="s">
+        <v>755</v>
+      </c>
+      <c r="M2" t="s">
+        <v>756</v>
+      </c>
+      <c r="N2" t="s">
+        <v>755</v>
+      </c>
+      <c r="O2" t="s">
         <v>757</v>
       </c>
-      <c r="H2" t="s">
+      <c r="P2" t="s">
         <v>758</v>
       </c>
-      <c r="I2" t="s">
-        <v>759</v>
-      </c>
-      <c r="J2" t="s">
-        <v>760</v>
-      </c>
-      <c r="K2" t="s">
-        <v>761</v>
-      </c>
-      <c r="L2" t="s">
-        <v>762</v>
-      </c>
-      <c r="M2" t="s">
-        <v>763</v>
-      </c>
-      <c r="N2" t="s">
-        <v>764</v>
-      </c>
-      <c r="O2" t="s">
-        <v>765</v>
-      </c>
-      <c r="P2" t="s">
-        <v>766</v>
-      </c>
       <c r="Q2" t="s">
-        <v>767</v>
+        <v>755</v>
       </c>
       <c r="R2" t="s">
         <v>96</v>
@@ -3183,101 +3072,22 @@
         <v>0</v>
       </c>
       <c r="X2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y2" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>769</v>
-      </c>
-      <c r="B3" t="s">
-        <v>754</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>770</v>
-      </c>
-      <c r="F3" t="s">
-        <v>771</v>
-      </c>
-      <c r="G3" t="s">
-        <v>772</v>
-      </c>
-      <c r="H3" t="s">
-        <v>773</v>
-      </c>
-      <c r="I3" t="s">
-        <v>774</v>
-      </c>
-      <c r="J3" t="s">
-        <v>774</v>
-      </c>
-      <c r="K3" t="s">
-        <v>775</v>
-      </c>
-      <c r="L3" t="s">
-        <v>774</v>
-      </c>
-      <c r="M3" t="s">
-        <v>776</v>
-      </c>
-      <c r="N3" t="s">
-        <v>774</v>
-      </c>
-      <c r="O3" t="s">
-        <v>765</v>
-      </c>
-      <c r="P3" t="s">
-        <v>777</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>778</v>
-      </c>
-      <c r="R3" t="s">
-        <v>96</v>
-      </c>
-      <c r="S3" t="s">
-        <v>79</v>
-      </c>
-      <c r="T3" t="s">
-        <v>80</v>
-      </c>
-      <c r="U3" t="s">
-        <v>754</v>
-      </c>
-      <c r="V3">
-        <f>IF(OR(ISBLANK(B3),TRIM(LOWER(X3))="completed",TRIM(LOWER(X3))="invalid",TRIM(LOWER(X3))="cancelled"),0,MAX(0,TODAY()-B3))</f>
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <f>IF(OR(ISBLANK(P3),TRIM(LOWER(X3))="completed",TRIM(LOWER(X3))="invalid",TRIM(LOWER(X3))="cancelled"),0,MAX(0,TODAY()-P3))</f>
-        <v>0</v>
-      </c>
-      <c r="X3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>768</v>
+        <v>759</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="8.85546875"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="4" width="18" customWidth="1"/>
@@ -3294,75 +3104,19 @@
         <v>37</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>753</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>753</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>769</v>
-      </c>
-      <c r="B4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>769</v>
-      </c>
-      <c r="B5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" t="s">
-        <v>780</v>
+        <v>760</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O4"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="8.85546875"/>
   <cols>
     <col min="1" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
@@ -3380,7 +3134,7 @@
   <sheetData>
     <row r="1" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>733</v>
@@ -3392,25 +3146,25 @@
         <v>37</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>783</v>
+        <v>762</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>784</v>
+        <v>763</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>785</v>
+        <v>764</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>786</v>
+        <v>765</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>787</v>
+        <v>766</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>788</v>
+        <v>767</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>789</v>
+        <v>768</v>
       </c>
       <c r="L1" s="10" t="s">
         <v>81</v>
@@ -3422,160 +3176,19 @@
         <v>106</v>
       </c>
       <c r="O1" s="10" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>791</v>
-      </c>
-      <c r="B2" t="s">
-        <v>753</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2" t="s">
-        <v>754</v>
-      </c>
-      <c r="F2" t="s">
-        <v>792</v>
-      </c>
-      <c r="G2" t="s">
-        <v>793</v>
-      </c>
-      <c r="H2" t="s">
-        <v>794</v>
-      </c>
-      <c r="I2">
-        <v>8.5</v>
-      </c>
-      <c r="J2" t="s">
-        <v>768</v>
-      </c>
-      <c r="K2" t="s">
-        <v>768</v>
-      </c>
-      <c r="L2" t="s">
-        <v>80</v>
-      </c>
-      <c r="M2" t="s">
-        <v>105</v>
-      </c>
-      <c r="N2" t="s">
-        <v>108</v>
-      </c>
-      <c r="O2" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>795</v>
-      </c>
-      <c r="B3" t="s">
-        <v>753</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" t="s">
-        <v>754</v>
-      </c>
-      <c r="F3" t="s">
-        <v>792</v>
-      </c>
-      <c r="G3" t="s">
-        <v>793</v>
-      </c>
-      <c r="H3" t="s">
-        <v>796</v>
-      </c>
-      <c r="I3">
-        <v>5.5</v>
-      </c>
-      <c r="J3" t="s">
-        <v>768</v>
-      </c>
-      <c r="K3" t="s">
-        <v>768</v>
-      </c>
-      <c r="L3" t="s">
-        <v>80</v>
-      </c>
-      <c r="M3" t="s">
-        <v>105</v>
-      </c>
-      <c r="N3" t="s">
-        <v>108</v>
-      </c>
-      <c r="O3" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>797</v>
-      </c>
-      <c r="B4" t="s">
-        <v>753</v>
-      </c>
-      <c r="C4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" t="s">
-        <v>754</v>
-      </c>
-      <c r="F4" t="s">
-        <v>792</v>
-      </c>
-      <c r="G4" t="s">
-        <v>793</v>
-      </c>
-      <c r="H4" t="s">
-        <v>798</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4" t="s">
-        <v>768</v>
-      </c>
-      <c r="K4" t="s">
-        <v>768</v>
-      </c>
-      <c r="L4" t="s">
-        <v>80</v>
-      </c>
-      <c r="M4" t="s">
-        <v>105</v>
-      </c>
-      <c r="N4" t="s">
-        <v>108</v>
-      </c>
-      <c r="O4" t="s">
-        <v>754</v>
+        <v>769</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="8.85546875"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -3595,69 +3208,37 @@
         <v>115</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>799</v>
+        <v>770</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>800</v>
+        <v>771</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>801</v>
+        <v>772</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>802</v>
+        <v>773</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>803</v>
+        <v>774</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>804</v>
+        <v>775</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>753</v>
-      </c>
-      <c r="B2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C2">
-        <v>2450</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <f>ROUND(C2*D2, 2)</f>
-        <v>4900</v>
-      </c>
-      <c r="F2">
-        <v>15</v>
-      </c>
-      <c r="G2">
-        <f>ROUND(E2-(E2*F2/100), 2)</f>
-        <v>4165</v>
-      </c>
-      <c r="H2">
-        <v>18</v>
-      </c>
-      <c r="I2">
-        <f>ROUND(G2+(G2*H2/100), 2)</f>
-        <v>4914.7</v>
+        <v>776</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M2"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="8.85546875"/>
   <cols>
     <col min="1" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
@@ -3674,96 +3255,55 @@
   <sheetData>
     <row r="1" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>806</v>
+        <v>777</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>733</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>807</v>
+        <v>778</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>808</v>
+        <v>779</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>809</v>
+        <v>780</v>
       </c>
       <c r="F1" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>810</v>
+        <v>781</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>811</v>
+        <v>782</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>812</v>
+        <v>783</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>813</v>
+        <v>784</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>814</v>
+        <v>785</v>
       </c>
       <c r="L1" s="10" t="s">
-        <v>815</v>
+        <v>786</v>
       </c>
       <c r="M1" s="10" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>817</v>
-      </c>
-      <c r="B2" t="s">
-        <v>753</v>
-      </c>
-      <c r="C2" t="s">
-        <v>754</v>
-      </c>
-      <c r="D2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" t="s">
-        <v>762</v>
-      </c>
-      <c r="H2" t="s">
-        <v>818</v>
-      </c>
-      <c r="I2">
-        <v>2500</v>
-      </c>
-      <c r="J2" t="s">
-        <v>819</v>
-      </c>
-      <c r="K2" t="s">
-        <v>79</v>
-      </c>
-      <c r="L2" t="s">
-        <v>96</v>
-      </c>
-      <c r="M2" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P3"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="8.85546875"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
@@ -3788,37 +3328,37 @@
         <v>0</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>821</v>
+        <v>788</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>822</v>
+        <v>789</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>823</v>
+        <v>790</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>824</v>
+        <v>791</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>825</v>
+        <v>792</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>826</v>
+        <v>793</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>827</v>
+        <v>794</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>814</v>
+        <v>785</v>
       </c>
       <c r="L1" s="10" t="s">
-        <v>829</v>
+        <v>796</v>
       </c>
       <c r="M1" s="10" t="s">
-        <v>790</v>
+        <v>769</v>
       </c>
       <c r="N1" s="10" t="s">
         <v>27</v>
@@ -3827,119 +3367,131 @@
         <v>752</v>
       </c>
       <c r="P1" s="10" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>753</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>754</v>
-      </c>
-      <c r="D2" t="s">
-        <v>831</v>
-      </c>
-      <c r="E2">
-        <v>15</v>
-      </c>
-      <c r="F2" t="s">
-        <v>781</v>
-      </c>
-      <c r="G2" t="s">
-        <v>780</v>
-      </c>
-      <c r="H2" t="s">
-        <v>780</v>
-      </c>
-      <c r="I2" t="s">
-        <v>768</v>
-      </c>
-      <c r="J2" t="s">
-        <v>768</v>
-      </c>
-      <c r="K2" t="s">
-        <v>79</v>
-      </c>
-      <c r="L2" t="s">
-        <v>96</v>
-      </c>
-      <c r="M2" t="s">
-        <v>754</v>
-      </c>
-      <c r="N2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O2" t="s">
-        <v>768</v>
-      </c>
-      <c r="P2" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>769</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>754</v>
-      </c>
-      <c r="D3" t="s">
-        <v>833</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" t="s">
-        <v>781</v>
-      </c>
-      <c r="G3" t="s">
-        <v>780</v>
-      </c>
-      <c r="H3" t="s">
-        <v>780</v>
-      </c>
-      <c r="I3" t="s">
-        <v>768</v>
-      </c>
-      <c r="J3" t="s">
-        <v>768</v>
-      </c>
-      <c r="K3" t="s">
-        <v>75</v>
-      </c>
-      <c r="L3" t="s">
-        <v>75</v>
-      </c>
-      <c r="M3" t="s">
-        <v>754</v>
-      </c>
-      <c r="N3" t="s">
-        <v>34</v>
-      </c>
-      <c r="O3" t="s">
-        <v>768</v>
-      </c>
-      <c r="P3" t="s">
-        <v>834</v>
+        <v>797</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="8.85546875"/>
+  <cols>
+    <col min="1" max="3" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="8.85546875"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
   </cols>
@@ -3991,14 +3543,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A10"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="8.85546875"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="8.85546875" customWidth="1"/>
@@ -4056,14 +3608,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A10"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="8.85546875"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
   </cols>
@@ -4120,14 +3672,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="8.85546875"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="3" width="20" customWidth="1"/>
@@ -4334,14 +3886,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="8.85546875"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="1"/>
     <col min="2" max="2" width="16.42578125" customWidth="1"/>
@@ -4515,14 +4067,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="8.85546875"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
   </cols>
@@ -4569,126 +4121,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="3" width="20" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>110</v>
-      </c>
-      <c r="B5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>111</v>
-      </c>
-      <c r="B6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>112</v>
-      </c>
-      <c r="B7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>113</v>
-      </c>
-      <c r="B8" t="s">
-        <v>105</v>
-      </c>
-      <c r="C8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B9" t="s">
-        <v>105</v>
-      </c>
-      <c r="C9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C618"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="8.85546875"/>
   <cols>
     <col min="1" max="1" width="90.42578125" customWidth="1"/>
     <col min="2" max="2" width="20.140625" customWidth="1"/>
@@ -4706,7 +4146,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>118</v>
       </c>
@@ -4717,7 +4157,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>120</v>
       </c>
@@ -4728,7 +4168,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>121</v>
       </c>
@@ -4739,7 +4179,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>122</v>
       </c>
@@ -4750,7 +4190,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>123</v>
       </c>
@@ -4761,7 +4201,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>124</v>
       </c>
@@ -4772,7 +4212,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>125</v>
       </c>
@@ -4783,7 +4223,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>126</v>
       </c>
@@ -4794,7 +4234,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>127</v>
       </c>
@@ -4805,7 +4245,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>128</v>
       </c>
@@ -4816,7 +4256,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>129</v>
       </c>
@@ -4827,7 +4267,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>130</v>
       </c>
@@ -4838,7 +4278,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>131</v>
       </c>
@@ -4849,7 +4289,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>132</v>
       </c>
@@ -4860,7 +4300,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>133</v>
       </c>
@@ -4871,7 +4311,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>134</v>
       </c>
@@ -4882,7 +4322,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>135</v>
       </c>
@@ -4893,7 +4333,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>136</v>
       </c>
@@ -4904,7 +4344,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>137</v>
       </c>
@@ -4915,7 +4355,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>138</v>
       </c>
@@ -4926,7 +4366,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>139</v>
       </c>
@@ -4937,7 +4377,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>140</v>
       </c>
@@ -4948,7 +4388,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>141</v>
       </c>
@@ -4959,7 +4399,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>142</v>
       </c>
@@ -4970,7 +4410,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>143</v>
       </c>
@@ -4981,7 +4421,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>144</v>
       </c>
@@ -4992,7 +4432,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>145</v>
       </c>
@@ -5003,7 +4443,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>146</v>
       </c>
@@ -5014,7 +4454,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>147</v>
       </c>
@@ -5025,7 +4465,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>148</v>
       </c>
@@ -5036,7 +4476,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>149</v>
       </c>
@@ -5047,7 +4487,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>150</v>
       </c>
@@ -5058,7 +4498,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>151</v>
       </c>
@@ -5069,7 +4509,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>152</v>
       </c>
@@ -5080,7 +4520,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>153</v>
       </c>
@@ -5091,7 +4531,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>154</v>
       </c>
@@ -5102,7 +4542,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>155</v>
       </c>
@@ -5113,7 +4553,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>156</v>
       </c>
@@ -5124,7 +4564,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
         <v>157</v>
       </c>
@@ -5135,7 +4575,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
         <v>158</v>
       </c>
@@ -5146,7 +4586,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
         <v>159</v>
       </c>
@@ -5157,7 +4597,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
         <v>160</v>
       </c>
@@ -5168,7 +4608,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>161</v>
       </c>
@@ -5179,7 +4619,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
         <v>162</v>
       </c>
@@ -5190,7 +4630,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>163</v>
       </c>
@@ -5201,7 +4641,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
         <v>164</v>
       </c>
@@ -5212,7 +4652,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>165</v>
       </c>
@@ -5223,7 +4663,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
         <v>166</v>
       </c>
@@ -5234,7 +4674,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>167</v>
       </c>
@@ -5245,7 +4685,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
         <v>168</v>
       </c>
@@ -5256,7 +4696,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>169</v>
       </c>
@@ -5267,7 +4707,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
         <v>170</v>
       </c>
@@ -5278,7 +4718,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
         <v>171</v>
       </c>
@@ -5289,7 +4729,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>172</v>
       </c>
@@ -5300,7 +4740,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
         <v>173</v>
       </c>
@@ -5311,7 +4751,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
         <v>174</v>
       </c>
@@ -5322,7 +4762,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
         <v>175</v>
       </c>
@@ -5333,7 +4773,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
         <v>176</v>
       </c>
@@ -5344,7 +4784,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
         <v>177</v>
       </c>
@@ -5355,7 +4795,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
         <v>178</v>
       </c>
@@ -5366,7 +4806,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
         <v>179</v>
       </c>
@@ -5377,7 +4817,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
         <v>180</v>
       </c>
@@ -5388,7 +4828,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
         <v>181</v>
       </c>
@@ -5399,7 +4839,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
         <v>182</v>
       </c>
@@ -5410,7 +4850,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
         <v>183</v>
       </c>
@@ -5421,7 +4861,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
         <v>184</v>
       </c>
@@ -5432,7 +4872,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
         <v>185</v>
       </c>
@@ -5443,7 +4883,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
         <v>186</v>
       </c>
@@ -5454,7 +4894,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
         <v>187</v>
       </c>
@@ -5465,7 +4905,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
         <v>188</v>
       </c>
@@ -5476,7 +4916,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
         <v>189</v>
       </c>
@@ -5487,7 +4927,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
         <v>190</v>
       </c>
@@ -5498,7 +4938,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
         <v>191</v>
       </c>
@@ -5509,7 +4949,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
         <v>192</v>
       </c>
@@ -5520,7 +4960,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
         <v>193</v>
       </c>
@@ -5531,7 +4971,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
         <v>194</v>
       </c>
@@ -5542,7 +4982,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
         <v>195</v>
       </c>
@@ -5553,7 +4993,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
         <v>196</v>
       </c>
@@ -5564,7 +5004,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
         <v>197</v>
       </c>
@@ -5575,7 +5015,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
         <v>198</v>
       </c>
@@ -5586,7 +5026,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
         <v>199</v>
       </c>
@@ -5597,7 +5037,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
         <v>200</v>
       </c>
@@ -5608,7 +5048,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
         <v>201</v>
       </c>
@@ -5619,7 +5059,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
         <v>202</v>
       </c>
@@ -5630,7 +5070,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
         <v>203</v>
       </c>
@@ -5641,7 +5081,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
         <v>204</v>
       </c>
@@ -5652,7 +5092,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
         <v>205</v>
       </c>
@@ -5663,7 +5103,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
         <v>206</v>
       </c>
@@ -5674,7 +5114,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
         <v>207</v>
       </c>
@@ -5685,7 +5125,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
         <v>208</v>
       </c>
@@ -5696,7 +5136,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
         <v>209</v>
       </c>
@@ -5707,7 +5147,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
         <v>210</v>
       </c>
@@ -5718,7 +5158,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
         <v>211</v>
       </c>
@@ -5729,7 +5169,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
         <v>212</v>
       </c>
@@ -5740,7 +5180,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
         <v>213</v>
       </c>
@@ -5751,7 +5191,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
         <v>214</v>
       </c>
@@ -5762,7 +5202,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
         <v>215</v>
       </c>
@@ -5773,7 +5213,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
         <v>216</v>
       </c>
@@ -5784,7 +5224,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
         <v>217</v>
       </c>
@@ -5795,7 +5235,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
         <v>218</v>
       </c>
@@ -5806,7 +5246,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
         <v>219</v>
       </c>
@@ -5817,7 +5257,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="6" t="s">
         <v>220</v>
       </c>
@@ -5828,7 +5268,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
         <v>221</v>
       </c>
@@ -5839,7 +5279,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
         <v>222</v>
       </c>
@@ -5850,7 +5290,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
         <v>223</v>
       </c>
@@ -5861,7 +5301,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="6" t="s">
         <v>224</v>
       </c>
@@ -5872,7 +5312,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
         <v>225</v>
       </c>
@@ -5883,7 +5323,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="6" t="s">
         <v>226</v>
       </c>
@@ -5894,7 +5334,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="6" t="s">
         <v>227</v>
       </c>
@@ -5905,7 +5345,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="6" t="s">
         <v>228</v>
       </c>
@@ -5916,7 +5356,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="6" t="s">
         <v>229</v>
       </c>
@@ -5927,7 +5367,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="6" t="s">
         <v>230</v>
       </c>
@@ -5938,7 +5378,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="6" t="s">
         <v>231</v>
       </c>
@@ -5949,7 +5389,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="6" t="s">
         <v>232</v>
       </c>
@@ -5960,7 +5400,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
         <v>233</v>
       </c>
@@ -5971,7 +5411,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="6" t="s">
         <v>234</v>
       </c>
@@ -5982,7 +5422,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="6" t="s">
         <v>235</v>
       </c>
@@ -5993,7 +5433,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="6" t="s">
         <v>236</v>
       </c>
@@ -6004,7 +5444,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
         <v>237</v>
       </c>
@@ -6015,7 +5455,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="6" t="s">
         <v>238</v>
       </c>
@@ -6026,7 +5466,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="6" t="s">
         <v>239</v>
       </c>
@@ -6037,7 +5477,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="6" t="s">
         <v>240</v>
       </c>
@@ -6048,7 +5488,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="6" t="s">
         <v>241</v>
       </c>
@@ -6059,7 +5499,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="6" t="s">
         <v>242</v>
       </c>
@@ -6070,7 +5510,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="6" t="s">
         <v>243</v>
       </c>
@@ -6081,7 +5521,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="6" t="s">
         <v>244</v>
       </c>
@@ -6092,7 +5532,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="6" t="s">
         <v>245</v>
       </c>
@@ -6103,7 +5543,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="6" t="s">
         <v>246</v>
       </c>
@@ -6114,7 +5554,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="6" t="s">
         <v>247</v>
       </c>
@@ -6125,7 +5565,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="6" t="s">
         <v>248</v>
       </c>
@@ -6136,7 +5576,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="6" t="s">
         <v>249</v>
       </c>
@@ -6147,7 +5587,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
         <v>250</v>
       </c>
@@ -6158,7 +5598,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="6" t="s">
         <v>251</v>
       </c>
@@ -6169,7 +5609,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="6" t="s">
         <v>252</v>
       </c>
@@ -6180,7 +5620,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="6" t="s">
         <v>253</v>
       </c>
@@ -6191,7 +5631,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="6" t="s">
         <v>254</v>
       </c>
@@ -6202,7 +5642,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="6" t="s">
         <v>255</v>
       </c>
@@ -6213,7 +5653,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="6" t="s">
         <v>256</v>
       </c>
@@ -6224,7 +5664,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="6" t="s">
         <v>257</v>
       </c>
@@ -6235,7 +5675,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="6" t="s">
         <v>258</v>
       </c>
@@ -6246,7 +5686,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="6" t="s">
         <v>259</v>
       </c>
@@ -6257,7 +5697,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="6" t="s">
         <v>260</v>
       </c>
@@ -6268,7 +5708,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="6" t="s">
         <v>261</v>
       </c>
@@ -6279,7 +5719,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="6" t="s">
         <v>262</v>
       </c>
@@ -6290,7 +5730,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="6" t="s">
         <v>263</v>
       </c>
@@ -6301,7 +5741,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="6" t="s">
         <v>264</v>
       </c>
@@ -6312,7 +5752,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="6" t="s">
         <v>265</v>
       </c>
@@ -6323,7 +5763,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="6" t="s">
         <v>266</v>
       </c>
@@ -6334,7 +5774,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
         <v>267</v>
       </c>
@@ -6345,7 +5785,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="6" t="s">
         <v>268</v>
       </c>
@@ -6356,7 +5796,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="6" t="s">
         <v>269</v>
       </c>
@@ -6367,7 +5807,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="6" t="s">
         <v>270</v>
       </c>
@@ -6378,7 +5818,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="6" t="s">
         <v>271</v>
       </c>
@@ -6389,7 +5829,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="6" t="s">
         <v>272</v>
       </c>
@@ -6400,7 +5840,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="6" t="s">
         <v>273</v>
       </c>
@@ -6411,7 +5851,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="6" t="s">
         <v>274</v>
       </c>
@@ -6422,7 +5862,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="6" t="s">
         <v>275</v>
       </c>
@@ -6433,7 +5873,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="6" t="s">
         <v>276</v>
       </c>
@@ -6444,7 +5884,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="6" t="s">
         <v>277</v>
       </c>
@@ -6455,7 +5895,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="6" t="s">
         <v>278</v>
       </c>
@@ -6466,7 +5906,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="6" t="s">
         <v>279</v>
       </c>
@@ -6477,7 +5917,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="6" t="s">
         <v>280</v>
       </c>
@@ -6488,7 +5928,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="6" t="s">
         <v>281</v>
       </c>
@@ -6499,7 +5939,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="6" t="s">
         <v>282</v>
       </c>
@@ -6510,7 +5950,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="6" t="s">
         <v>283</v>
       </c>
@@ -6521,7 +5961,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="6" t="s">
         <v>284</v>
       </c>
@@ -6532,7 +5972,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
         <v>285</v>
       </c>
@@ -6543,7 +5983,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="6" t="s">
         <v>286</v>
       </c>
@@ -6554,7 +5994,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="6" t="s">
         <v>287</v>
       </c>
@@ -6565,7 +6005,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="6" t="s">
         <v>288</v>
       </c>
@@ -6576,7 +6016,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="6" t="s">
         <v>289</v>
       </c>
@@ -6587,7 +6027,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="6" t="s">
         <v>290</v>
       </c>
@@ -6598,7 +6038,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="6" t="s">
         <v>291</v>
       </c>
@@ -6609,7 +6049,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="6" t="s">
         <v>292</v>
       </c>
@@ -6620,7 +6060,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="6" t="s">
         <v>293</v>
       </c>
@@ -6631,7 +6071,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="6" t="s">
         <v>294</v>
       </c>
@@ -6642,7 +6082,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="6" t="s">
         <v>295</v>
       </c>
@@ -6653,7 +6093,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="6" t="s">
         <v>296</v>
       </c>
@@ -6664,7 +6104,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="6" t="s">
         <v>297</v>
       </c>
@@ -6675,7 +6115,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="6" t="s">
         <v>298</v>
       </c>
@@ -6686,7 +6126,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="6" t="s">
         <v>299</v>
       </c>
@@ -6697,7 +6137,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="6" t="s">
         <v>300</v>
       </c>
@@ -6708,7 +6148,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="6" t="s">
         <v>301</v>
       </c>
@@ -6719,7 +6159,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
         <v>302</v>
       </c>
@@ -6730,7 +6170,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="6" t="s">
         <v>303</v>
       </c>
@@ -6741,7 +6181,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="6" t="s">
         <v>304</v>
       </c>
@@ -6752,7 +6192,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="6" t="s">
         <v>305</v>
       </c>
@@ -6763,7 +6203,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="6" t="s">
         <v>306</v>
       </c>
@@ -6774,7 +6214,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="6" t="s">
         <v>307</v>
       </c>
@@ -6785,7 +6225,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="6" t="s">
         <v>308</v>
       </c>
@@ -6796,7 +6236,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="6" t="s">
         <v>309</v>
       </c>
@@ -6807,7 +6247,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="6" t="s">
         <v>310</v>
       </c>
@@ -6818,7 +6258,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="6" t="s">
         <v>311</v>
       </c>
@@ -6829,7 +6269,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="6" t="s">
         <v>312</v>
       </c>
@@ -6840,7 +6280,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="6" t="s">
         <v>313</v>
       </c>
@@ -6851,7 +6291,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="6" t="s">
         <v>314</v>
       </c>
@@ -6862,7 +6302,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="6" t="s">
         <v>315</v>
       </c>
@@ -6873,7 +6313,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="6" t="s">
         <v>316</v>
       </c>
@@ -6884,7 +6324,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="6" t="s">
         <v>317</v>
       </c>
@@ -6895,7 +6335,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
         <v>318</v>
       </c>
@@ -6906,7 +6346,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="6" t="s">
         <v>319</v>
       </c>
@@ -6917,7 +6357,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" s="6" t="s">
         <v>320</v>
       </c>
@@ -6928,7 +6368,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" s="6" t="s">
         <v>321</v>
       </c>
@@ -6939,7 +6379,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="6" t="s">
         <v>322</v>
       </c>
@@ -6950,7 +6390,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="206" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" s="6" t="s">
         <v>323</v>
       </c>
@@ -6961,7 +6401,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="207" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" s="6" t="s">
         <v>324</v>
       </c>
@@ -6972,7 +6412,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" s="6" t="s">
         <v>325</v>
       </c>
@@ -6983,7 +6423,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="209" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="6" t="s">
         <v>326</v>
       </c>
@@ -6994,7 +6434,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="6" t="s">
         <v>327</v>
       </c>
@@ -7005,7 +6445,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="6" t="s">
         <v>328</v>
       </c>
@@ -7016,7 +6456,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="6" t="s">
         <v>329</v>
       </c>
@@ -7027,7 +6467,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" s="6" t="s">
         <v>330</v>
       </c>
@@ -7038,7 +6478,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" s="6" t="s">
         <v>331</v>
       </c>
@@ -7049,7 +6489,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="6" t="s">
         <v>332</v>
       </c>
@@ -7060,7 +6500,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="6" t="s">
         <v>333</v>
       </c>
@@ -7071,7 +6511,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="6" t="s">
         <v>334</v>
       </c>
@@ -7082,7 +6522,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" s="6" t="s">
         <v>335</v>
       </c>
@@ -7093,7 +6533,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="6" t="s">
         <v>336</v>
       </c>
@@ -7104,7 +6544,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
         <v>337</v>
       </c>
@@ -7115,7 +6555,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" s="6" t="s">
         <v>338</v>
       </c>
@@ -7126,7 +6566,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" s="6" t="s">
         <v>339</v>
       </c>
@@ -7137,7 +6577,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="223" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="6" t="s">
         <v>340</v>
       </c>
@@ -7148,7 +6588,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" s="6" t="s">
         <v>341</v>
       </c>
@@ -7159,7 +6599,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" s="6" t="s">
         <v>342</v>
       </c>
@@ -7170,7 +6610,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="226" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" s="6" t="s">
         <v>343</v>
       </c>
@@ -7181,7 +6621,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="227" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" s="6" t="s">
         <v>344</v>
       </c>
@@ -7192,7 +6632,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="228" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" s="6" t="s">
         <v>345</v>
       </c>
@@ -7203,7 +6643,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="229" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" s="6" t="s">
         <v>346</v>
       </c>
@@ -7214,7 +6654,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="230" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" s="6" t="s">
         <v>347</v>
       </c>
@@ -7225,7 +6665,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="231" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" s="6" t="s">
         <v>348</v>
       </c>
@@ -7236,7 +6676,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="232" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" s="6" t="s">
         <v>349</v>
       </c>
@@ -7247,7 +6687,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="233" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" s="6" t="s">
         <v>350</v>
       </c>
@@ -7258,7 +6698,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="234" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" s="6" t="s">
         <v>351</v>
       </c>
@@ -7269,7 +6709,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="235" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" s="6" t="s">
         <v>352</v>
       </c>
@@ -7280,7 +6720,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="236" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" s="6" t="s">
         <v>353</v>
       </c>
@@ -7291,7 +6731,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="237" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
         <v>354</v>
       </c>
@@ -7302,7 +6742,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="238" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" s="6" t="s">
         <v>355</v>
       </c>
@@ -7313,7 +6753,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="239" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" s="6" t="s">
         <v>356</v>
       </c>
@@ -7324,7 +6764,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="240" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" s="6" t="s">
         <v>357</v>
       </c>
@@ -7335,7 +6775,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="241" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" s="6" t="s">
         <v>358</v>
       </c>
@@ -7346,7 +6786,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="242" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" s="6" t="s">
         <v>359</v>
       </c>
@@ -7357,7 +6797,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="243" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" s="6" t="s">
         <v>360</v>
       </c>
@@ -7368,7 +6808,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="244" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" s="6" t="s">
         <v>361</v>
       </c>
@@ -7379,7 +6819,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="245" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" s="6" t="s">
         <v>362</v>
       </c>
@@ -7390,7 +6830,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="246" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" s="6" t="s">
         <v>363</v>
       </c>
@@ -7401,7 +6841,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="247" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" s="6" t="s">
         <v>364</v>
       </c>
@@ -7412,7 +6852,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="248" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" s="6" t="s">
         <v>365</v>
       </c>
@@ -7423,7 +6863,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="249" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" s="6" t="s">
         <v>366</v>
       </c>
@@ -7434,7 +6874,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="250" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" s="6" t="s">
         <v>367</v>
       </c>
@@ -7445,7 +6885,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="251" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" s="6" t="s">
         <v>368</v>
       </c>
@@ -7456,7 +6896,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="252" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" s="6" t="s">
         <v>369</v>
       </c>
@@ -7467,7 +6907,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="253" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" s="6" t="s">
         <v>370</v>
       </c>
@@ -7478,7 +6918,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="254" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" s="6" t="s">
         <v>371</v>
       </c>
@@ -7489,7 +6929,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="255" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
         <v>372</v>
       </c>
@@ -7500,7 +6940,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="256" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" s="6" t="s">
         <v>373</v>
       </c>
@@ -7511,7 +6951,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="257" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" s="6" t="s">
         <v>374</v>
       </c>
@@ -7522,7 +6962,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="258" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" s="6" t="s">
         <v>375</v>
       </c>
@@ -7533,7 +6973,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="259" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" s="6" t="s">
         <v>376</v>
       </c>
@@ -7544,7 +6984,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="260" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" s="6" t="s">
         <v>377</v>
       </c>
@@ -7555,7 +6995,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="261" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" s="6" t="s">
         <v>378</v>
       </c>
@@ -7566,7 +7006,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="262" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" s="6" t="s">
         <v>379</v>
       </c>
@@ -7577,7 +7017,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="263" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" s="6" t="s">
         <v>380</v>
       </c>
@@ -7588,7 +7028,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="264" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" s="6" t="s">
         <v>381</v>
       </c>
@@ -7599,7 +7039,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="265" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" s="6" t="s">
         <v>382</v>
       </c>
@@ -7610,7 +7050,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="266" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" s="6" t="s">
         <v>383</v>
       </c>
@@ -7621,7 +7061,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="267" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" s="6" t="s">
         <v>384</v>
       </c>
@@ -7632,7 +7072,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="268" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" s="6" t="s">
         <v>385</v>
       </c>
@@ -7643,7 +7083,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="269" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" s="6" t="s">
         <v>386</v>
       </c>
@@ -7654,7 +7094,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="270" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" s="6" t="s">
         <v>387</v>
       </c>
@@ -7665,7 +7105,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="271" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" s="6" t="s">
         <v>388</v>
       </c>
@@ -7676,7 +7116,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="272" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" s="6" t="s">
         <v>389</v>
       </c>
@@ -7687,7 +7127,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="273" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" s="6" t="s">
         <v>390</v>
       </c>
@@ -7698,7 +7138,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="274" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
         <v>391</v>
       </c>
@@ -7709,7 +7149,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="275" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" s="6" t="s">
         <v>392</v>
       </c>
@@ -7720,7 +7160,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="276" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" s="6" t="s">
         <v>393</v>
       </c>
@@ -7731,7 +7171,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="277" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" s="6" t="s">
         <v>394</v>
       </c>
@@ -7742,7 +7182,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="278" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" s="6" t="s">
         <v>395</v>
       </c>
@@ -7753,7 +7193,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="279" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" s="6" t="s">
         <v>396</v>
       </c>
@@ -7764,7 +7204,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="280" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" s="6" t="s">
         <v>397</v>
       </c>
@@ -7775,7 +7215,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="281" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" s="6" t="s">
         <v>398</v>
       </c>
@@ -7786,7 +7226,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="282" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" s="6" t="s">
         <v>399</v>
       </c>
@@ -7797,7 +7237,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="283" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" s="6" t="s">
         <v>400</v>
       </c>
@@ -7808,7 +7248,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="284" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" s="6" t="s">
         <v>401</v>
       </c>
@@ -7819,7 +7259,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="285" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" s="6" t="s">
         <v>402</v>
       </c>
@@ -7830,7 +7270,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="286" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" s="6" t="s">
         <v>403</v>
       </c>
@@ -7841,7 +7281,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="287" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" s="6" t="s">
         <v>404</v>
       </c>
@@ -7852,7 +7292,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="288" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" s="6" t="s">
         <v>405</v>
       </c>
@@ -7863,7 +7303,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="289" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" s="6" t="s">
         <v>406</v>
       </c>
@@ -7874,7 +7314,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="290" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" s="6" t="s">
         <v>407</v>
       </c>
@@ -7885,7 +7325,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="291" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" s="6" t="s">
         <v>408</v>
       </c>
@@ -7896,7 +7336,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="292" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" s="6" t="s">
         <v>409</v>
       </c>
@@ -7907,7 +7347,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="293" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293" s="6" t="s">
         <v>410</v>
       </c>
@@ -7918,7 +7358,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="294" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294" s="6" t="s">
         <v>411</v>
       </c>
@@ -7929,7 +7369,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="295" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" s="6" t="s">
         <v>412</v>
       </c>
@@ -7940,7 +7380,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="296" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296" s="6" t="s">
         <v>413</v>
       </c>
@@ -7951,7 +7391,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="297" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" s="6" t="s">
         <v>414</v>
       </c>
@@ -7962,7 +7402,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="298" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" s="6" t="s">
         <v>415</v>
       </c>
@@ -7973,7 +7413,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="299" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299" s="6" t="s">
         <v>416</v>
       </c>
@@ -7984,7 +7424,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="300" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300" s="6" t="s">
         <v>417</v>
       </c>
@@ -7995,7 +7435,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="301" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" s="6" t="s">
         <v>418</v>
       </c>
@@ -8006,7 +7446,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="302" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" s="6" t="s">
         <v>419</v>
       </c>
@@ -8017,7 +7457,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="303" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303" s="6" t="s">
         <v>420</v>
       </c>
@@ -8028,7 +7468,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="304" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" s="6" t="s">
         <v>421</v>
       </c>
@@ -8039,7 +7479,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="305" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" s="6" t="s">
         <v>422</v>
       </c>
@@ -8050,7 +7490,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="306" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" s="6" t="s">
         <v>423</v>
       </c>
@@ -8061,7 +7501,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="307" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" s="6" t="s">
         <v>424</v>
       </c>
@@ -8072,7 +7512,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="308" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" s="6" t="s">
         <v>425</v>
       </c>
@@ -8083,7 +7523,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="309" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309" s="6" t="s">
         <v>426</v>
       </c>
@@ -8094,7 +7534,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="310" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310" s="6" t="s">
         <v>427</v>
       </c>
@@ -8105,7 +7545,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="311" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" s="6" t="s">
         <v>428</v>
       </c>
@@ -8116,7 +7556,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="312" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" s="6" t="s">
         <v>429</v>
       </c>
@@ -8127,7 +7567,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="313" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313" s="6" t="s">
         <v>430</v>
       </c>
@@ -8138,7 +7578,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="314" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314" s="6" t="s">
         <v>431</v>
       </c>
@@ -8149,7 +7589,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="315" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315" s="6" t="s">
         <v>432</v>
       </c>
@@ -8160,7 +7600,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="316" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316" s="6" t="s">
         <v>433</v>
       </c>
@@ -8171,7 +7611,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="317" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317" s="6" t="s">
         <v>434</v>
       </c>
@@ -8182,7 +7622,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="318" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318" s="6" t="s">
         <v>435</v>
       </c>
@@ -8193,7 +7633,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="319" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319" s="6" t="s">
         <v>124</v>
       </c>
@@ -8204,7 +7644,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="320" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320" s="6" t="s">
         <v>436</v>
       </c>
@@ -8215,7 +7655,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="321" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321" s="6" t="s">
         <v>437</v>
       </c>
@@ -8226,7 +7666,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="322" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322" s="6" t="s">
         <v>438</v>
       </c>
@@ -8237,7 +7677,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="323" spans="1:3" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" ht="32.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" s="6" t="s">
         <v>439</v>
       </c>
@@ -8248,7 +7688,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="324" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324" s="6" t="s">
         <v>440</v>
       </c>
@@ -8259,7 +7699,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="325" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325" s="6" t="s">
         <v>441</v>
       </c>
@@ -8270,7 +7710,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="326" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326" s="6" t="s">
         <v>442</v>
       </c>
@@ -8281,7 +7721,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="327" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" s="6" t="s">
         <v>443</v>
       </c>
@@ -8292,7 +7732,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="328" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" s="6" t="s">
         <v>444</v>
       </c>
@@ -8303,7 +7743,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="329" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329" s="6" t="s">
         <v>445</v>
       </c>
@@ -8314,7 +7754,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="330" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330" s="6" t="s">
         <v>446</v>
       </c>
@@ -8325,7 +7765,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="331" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331" s="6" t="s">
         <v>447</v>
       </c>
@@ -8336,7 +7776,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="332" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332" s="6" t="s">
         <v>448</v>
       </c>
@@ -8347,7 +7787,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="333" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333" s="6" t="s">
         <v>449</v>
       </c>
@@ -8358,7 +7798,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="334" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334" s="6" t="s">
         <v>450</v>
       </c>
@@ -8369,7 +7809,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="335" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335" s="6" t="s">
         <v>451</v>
       </c>
@@ -8380,7 +7820,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="336" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336" s="6" t="s">
         <v>452</v>
       </c>
@@ -8391,7 +7831,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="337" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337" s="6" t="s">
         <v>453</v>
       </c>
@@ -8402,7 +7842,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="338" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338" s="6" t="s">
         <v>454</v>
       </c>
@@ -8413,7 +7853,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="339" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339" s="6" t="s">
         <v>455</v>
       </c>
@@ -8435,7 +7875,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="341" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" s="6" t="s">
         <v>118</v>
       </c>
@@ -8446,7 +7886,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="342" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342" s="6" t="s">
         <v>120</v>
       </c>
@@ -8457,7 +7897,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="343" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343" s="6" t="s">
         <v>457</v>
       </c>
@@ -8468,7 +7908,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="344" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344" s="6" t="s">
         <v>458</v>
       </c>
@@ -8479,7 +7919,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="345" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345" s="6" t="s">
         <v>459</v>
       </c>
@@ -8490,7 +7930,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="346" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346" s="6" t="s">
         <v>460</v>
       </c>
@@ -8501,7 +7941,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="347" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347" s="6" t="s">
         <v>461</v>
       </c>
@@ -8512,7 +7952,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="348" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348" s="6" t="s">
         <v>462</v>
       </c>
@@ -8523,7 +7963,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="349" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349" s="6" t="s">
         <v>463</v>
       </c>
@@ -8534,7 +7974,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="350" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350" s="6" t="s">
         <v>464</v>
       </c>
@@ -8545,7 +7985,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="351" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351" s="6" t="s">
         <v>465</v>
       </c>
@@ -8556,7 +7996,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="352" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352" s="6" t="s">
         <v>466</v>
       </c>
@@ -8567,7 +8007,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="353" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A353" s="6" t="s">
         <v>467</v>
       </c>
@@ -8578,7 +8018,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="354" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A354" s="6" t="s">
         <v>468</v>
       </c>
@@ -8589,7 +8029,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="355" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A355" s="6" t="s">
         <v>469</v>
       </c>
@@ -8600,7 +8040,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="356" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356" s="6" t="s">
         <v>470</v>
       </c>
@@ -8611,7 +8051,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="357" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357" s="6" t="s">
         <v>471</v>
       </c>
@@ -8622,7 +8062,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="358" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A358" s="6" t="s">
         <v>472</v>
       </c>
@@ -8633,7 +8073,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="359" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359" s="6" t="s">
         <v>473</v>
       </c>
@@ -8644,7 +8084,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="360" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A360" s="6" t="s">
         <v>474</v>
       </c>
@@ -8655,7 +8095,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="361" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361" s="6" t="s">
         <v>475</v>
       </c>
@@ -8666,7 +8106,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="362" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362" s="6" t="s">
         <v>476</v>
       </c>
@@ -8677,7 +8117,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="363" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A363" s="6" t="s">
         <v>477</v>
       </c>
@@ -8688,7 +8128,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="364" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364" s="6" t="s">
         <v>478</v>
       </c>
@@ -8699,7 +8139,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="365" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365" s="6" t="s">
         <v>479</v>
       </c>
@@ -8710,7 +8150,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="366" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366" s="6" t="s">
         <v>480</v>
       </c>
@@ -8721,7 +8161,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="367" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367" s="6" t="s">
         <v>481</v>
       </c>
@@ -8732,7 +8172,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="368" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368" s="6" t="s">
         <v>482</v>
       </c>
@@ -8743,7 +8183,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="369" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369" s="6" t="s">
         <v>483</v>
       </c>
@@ -8754,7 +8194,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="370" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A370" s="6" t="s">
         <v>484</v>
       </c>
@@ -8765,7 +8205,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="371" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371" s="6" t="s">
         <v>485</v>
       </c>
@@ -8776,7 +8216,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="372" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372" s="6" t="s">
         <v>486</v>
       </c>
@@ -8787,7 +8227,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="373" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373" s="6" t="s">
         <v>487</v>
       </c>
@@ -8798,7 +8238,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="374" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A374" s="6" t="s">
         <v>488</v>
       </c>
@@ -8809,7 +8249,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="375" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375" s="6" t="s">
         <v>489</v>
       </c>
@@ -8820,7 +8260,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="376" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A376" s="6" t="s">
         <v>490</v>
       </c>
@@ -8831,7 +8271,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="377" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377" s="6" t="s">
         <v>491</v>
       </c>
@@ -8842,7 +8282,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="378" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A378" s="6" t="s">
         <v>492</v>
       </c>
@@ -8853,7 +8293,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="379" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A379" s="6" t="s">
         <v>493</v>
       </c>
@@ -8864,7 +8304,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="380" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A380" s="6" t="s">
         <v>494</v>
       </c>
@@ -8875,7 +8315,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="381" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A381" s="6" t="s">
         <v>495</v>
       </c>
@@ -8886,7 +8326,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="382" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A382" s="6" t="s">
         <v>496</v>
       </c>
@@ -8897,7 +8337,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="383" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A383" s="6" t="s">
         <v>497</v>
       </c>
@@ -8908,7 +8348,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="384" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A384" s="6" t="s">
         <v>498</v>
       </c>
@@ -8919,7 +8359,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="385" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A385" s="6" t="s">
         <v>499</v>
       </c>
@@ -8930,7 +8370,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="386" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A386" s="6" t="s">
         <v>500</v>
       </c>
@@ -8941,7 +8381,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="387" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A387" s="6" t="s">
         <v>501</v>
       </c>
@@ -8952,7 +8392,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="388" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A388" s="6" t="s">
         <v>502</v>
       </c>
@@ -8963,7 +8403,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="389" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A389" s="6" t="s">
         <v>503</v>
       </c>
@@ -8974,7 +8414,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="390" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A390" s="6" t="s">
         <v>504</v>
       </c>
@@ -8985,7 +8425,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="391" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A391" s="6" t="s">
         <v>505</v>
       </c>
@@ -8996,7 +8436,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="392" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A392" s="6" t="s">
         <v>506</v>
       </c>
@@ -9007,7 +8447,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="393" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A393" s="6" t="s">
         <v>507</v>
       </c>
@@ -9018,7 +8458,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="394" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A394" s="6" t="s">
         <v>508</v>
       </c>
@@ -9029,7 +8469,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="395" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A395" s="6" t="s">
         <v>509</v>
       </c>
@@ -9040,7 +8480,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="396" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A396" s="6" t="s">
         <v>510</v>
       </c>
@@ -9051,7 +8491,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="397" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A397" s="6" t="s">
         <v>511</v>
       </c>
@@ -9062,7 +8502,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="398" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A398" s="6" t="s">
         <v>512</v>
       </c>
@@ -9073,7 +8513,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="399" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A399" s="6" t="s">
         <v>513</v>
       </c>
@@ -9084,7 +8524,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="400" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A400" s="6" t="s">
         <v>514</v>
       </c>
@@ -9095,7 +8535,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="401" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A401" s="6" t="s">
         <v>515</v>
       </c>
@@ -9106,7 +8546,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="402" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A402" s="6" t="s">
         <v>516</v>
       </c>
@@ -9117,7 +8557,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="403" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A403" s="6" t="s">
         <v>517</v>
       </c>
@@ -9128,7 +8568,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="404" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404" s="6" t="s">
         <v>518</v>
       </c>
@@ -9139,7 +8579,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="405" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A405" s="6" t="s">
         <v>519</v>
       </c>
@@ -9150,7 +8590,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="406" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A406" s="6" t="s">
         <v>520</v>
       </c>
@@ -9161,7 +8601,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="407" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A407" s="6" t="s">
         <v>521</v>
       </c>
@@ -9172,7 +8612,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="408" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A408" s="6" t="s">
         <v>522</v>
       </c>
@@ -9183,7 +8623,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="409" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A409" s="6" t="s">
         <v>523</v>
       </c>
@@ -9194,7 +8634,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="410" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A410" s="6" t="s">
         <v>524</v>
       </c>
@@ -9205,7 +8645,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="411" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A411" s="6" t="s">
         <v>525</v>
       </c>
@@ -9216,7 +8656,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="412" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A412" s="6" t="s">
         <v>526</v>
       </c>
@@ -9227,7 +8667,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="413" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A413" s="6" t="s">
         <v>527</v>
       </c>
@@ -9238,7 +8678,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="414" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A414" s="6" t="s">
         <v>528</v>
       </c>
@@ -9249,7 +8689,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="415" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A415" s="6" t="s">
         <v>529</v>
       </c>
@@ -9260,7 +8700,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="416" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A416" s="6" t="s">
         <v>530</v>
       </c>
@@ -9271,7 +8711,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="417" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A417" s="6" t="s">
         <v>531</v>
       </c>
@@ -9282,7 +8722,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="418" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A418" s="6" t="s">
         <v>532</v>
       </c>
@@ -9293,7 +8733,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="419" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A419" s="6" t="s">
         <v>533</v>
       </c>
@@ -9304,7 +8744,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="420" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A420" s="6" t="s">
         <v>534</v>
       </c>
@@ -9315,7 +8755,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="421" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A421" s="6" t="s">
         <v>535</v>
       </c>
@@ -9326,7 +8766,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="422" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A422" s="6" t="s">
         <v>536</v>
       </c>
@@ -9337,7 +8777,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="423" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A423" s="6" t="s">
         <v>537</v>
       </c>
@@ -9348,7 +8788,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="424" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A424" s="6" t="s">
         <v>538</v>
       </c>
@@ -9359,7 +8799,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="425" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A425" s="6" t="s">
         <v>539</v>
       </c>
@@ -9370,7 +8810,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="426" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A426" s="6" t="s">
         <v>540</v>
       </c>
@@ -9381,7 +8821,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="427" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A427" s="6" t="s">
         <v>541</v>
       </c>
@@ -9392,7 +8832,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="428" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A428" s="6" t="s">
         <v>542</v>
       </c>
@@ -9403,7 +8843,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="429" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A429" s="6" t="s">
         <v>543</v>
       </c>
@@ -9414,7 +8854,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="430" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A430" s="6" t="s">
         <v>544</v>
       </c>
@@ -9425,7 +8865,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="431" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A431" s="6" t="s">
         <v>545</v>
       </c>
@@ -9436,7 +8876,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="432" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A432" s="6" t="s">
         <v>546</v>
       </c>
@@ -9447,7 +8887,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="433" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A433" s="6" t="s">
         <v>547</v>
       </c>
@@ -9458,7 +8898,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="434" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A434" s="6" t="s">
         <v>548</v>
       </c>
@@ -9469,7 +8909,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="435" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A435" s="6" t="s">
         <v>549</v>
       </c>
@@ -9480,7 +8920,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="436" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A436" s="6" t="s">
         <v>550</v>
       </c>
@@ -9491,7 +8931,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="437" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A437" s="6" t="s">
         <v>551</v>
       </c>
@@ -9502,7 +8942,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="438" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A438" s="6" t="s">
         <v>552</v>
       </c>
@@ -9513,7 +8953,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="439" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A439" s="6" t="s">
         <v>553</v>
       </c>
@@ -9524,7 +8964,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="440" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A440" s="6" t="s">
         <v>554</v>
       </c>
@@ -9535,7 +8975,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="441" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A441" s="6" t="s">
         <v>555</v>
       </c>
@@ -9546,7 +8986,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="442" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A442" s="6" t="s">
         <v>556</v>
       </c>
@@ -9557,7 +8997,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="443" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A443" s="6" t="s">
         <v>557</v>
       </c>
@@ -9568,7 +9008,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="444" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A444" s="6" t="s">
         <v>558</v>
       </c>
@@ -9579,7 +9019,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="445" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A445" s="6" t="s">
         <v>559</v>
       </c>
@@ -9590,7 +9030,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="446" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A446" s="6" t="s">
         <v>560</v>
       </c>
@@ -9601,7 +9041,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="447" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A447" s="6" t="s">
         <v>561</v>
       </c>
@@ -9612,7 +9052,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="448" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A448" s="6" t="s">
         <v>562</v>
       </c>
@@ -9623,7 +9063,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="449" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A449" s="6" t="s">
         <v>563</v>
       </c>
@@ -9634,7 +9074,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="450" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A450" s="6" t="s">
         <v>564</v>
       </c>
@@ -9645,7 +9085,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="451" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A451" s="6" t="s">
         <v>565</v>
       </c>
@@ -9656,7 +9096,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="452" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A452" s="6" t="s">
         <v>566</v>
       </c>
@@ -9667,7 +9107,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="453" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A453" s="6" t="s">
         <v>567</v>
       </c>
@@ -9678,7 +9118,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="454" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A454" s="6" t="s">
         <v>568</v>
       </c>
@@ -9689,7 +9129,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="455" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A455" s="6" t="s">
         <v>569</v>
       </c>
@@ -9700,7 +9140,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="456" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A456" s="6" t="s">
         <v>570</v>
       </c>
@@ -9711,7 +9151,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="457" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A457" s="6" t="s">
         <v>571</v>
       </c>
@@ -9722,7 +9162,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="458" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A458" s="6" t="s">
         <v>572</v>
       </c>
@@ -9733,7 +9173,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="459" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A459" s="6" t="s">
         <v>573</v>
       </c>
@@ -9744,7 +9184,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="460" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A460" s="6" t="s">
         <v>574</v>
       </c>
@@ -9755,7 +9195,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="461" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A461" s="6" t="s">
         <v>575</v>
       </c>
@@ -9766,7 +9206,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="462" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A462" s="6" t="s">
         <v>576</v>
       </c>
@@ -9777,7 +9217,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="463" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A463" s="6" t="s">
         <v>577</v>
       </c>
@@ -9788,7 +9228,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="464" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A464" s="6" t="s">
         <v>578</v>
       </c>
@@ -9799,7 +9239,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="465" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A465" s="6" t="s">
         <v>579</v>
       </c>
@@ -9810,7 +9250,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="466" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A466" s="6" t="s">
         <v>580</v>
       </c>
@@ -9821,7 +9261,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="467" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A467" s="6" t="s">
         <v>581</v>
       </c>
@@ -9832,7 +9272,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="468" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A468" s="6" t="s">
         <v>582</v>
       </c>
@@ -9843,7 +9283,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="469" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A469" s="6" t="s">
         <v>583</v>
       </c>
@@ -9854,7 +9294,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="470" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A470" s="6" t="s">
         <v>584</v>
       </c>
@@ -9865,7 +9305,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="471" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A471" s="6" t="s">
         <v>585</v>
       </c>
@@ -9876,7 +9316,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="472" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A472" s="6" t="s">
         <v>586</v>
       </c>
@@ -9887,7 +9327,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="473" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A473" s="6" t="s">
         <v>587</v>
       </c>
@@ -9898,7 +9338,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="474" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A474" s="6" t="s">
         <v>588</v>
       </c>
@@ -9909,7 +9349,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="475" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A475" s="6" t="s">
         <v>589</v>
       </c>
@@ -9920,7 +9360,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="476" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A476" s="6" t="s">
         <v>590</v>
       </c>
@@ -9931,7 +9371,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="477" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A477" s="6" t="s">
         <v>591</v>
       </c>
@@ -9942,7 +9382,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="478" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A478" s="6" t="s">
         <v>592</v>
       </c>
@@ -9953,7 +9393,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="479" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A479" s="6" t="s">
         <v>593</v>
       </c>
@@ -9964,7 +9404,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="480" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A480" s="6" t="s">
         <v>594</v>
       </c>
@@ -9975,7 +9415,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="481" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A481" s="6" t="s">
         <v>595</v>
       </c>
@@ -9986,7 +9426,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="482" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A482" s="6" t="s">
         <v>596</v>
       </c>
@@ -9997,7 +9437,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="483" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A483" s="6" t="s">
         <v>597</v>
       </c>
@@ -10008,7 +9448,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="484" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A484" s="6" t="s">
         <v>598</v>
       </c>
@@ -10019,7 +9459,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="485" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A485" s="6" t="s">
         <v>599</v>
       </c>
@@ -10030,7 +9470,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="486" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A486" s="6" t="s">
         <v>600</v>
       </c>
@@ -10041,7 +9481,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="487" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A487" s="6" t="s">
         <v>601</v>
       </c>
@@ -10052,7 +9492,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="488" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A488" s="6" t="s">
         <v>602</v>
       </c>
@@ -10063,7 +9503,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="489" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A489" s="6" t="s">
         <v>603</v>
       </c>
@@ -10074,7 +9514,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="490" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A490" s="6" t="s">
         <v>604</v>
       </c>
@@ -10085,7 +9525,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="491" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A491" s="6" t="s">
         <v>605</v>
       </c>
@@ -10096,7 +9536,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="492" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A492" s="6" t="s">
         <v>606</v>
       </c>
@@ -10107,7 +9547,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="493" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A493" s="6" t="s">
         <v>607</v>
       </c>
@@ -10118,7 +9558,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="494" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A494" s="6" t="s">
         <v>608</v>
       </c>
@@ -10129,7 +9569,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="495" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A495" s="6" t="s">
         <v>609</v>
       </c>
@@ -10140,7 +9580,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="496" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A496" s="6" t="s">
         <v>610</v>
       </c>
@@ -10151,7 +9591,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="497" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A497" s="6" t="s">
         <v>611</v>
       </c>
@@ -10162,7 +9602,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="498" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A498" s="6" t="s">
         <v>612</v>
       </c>
@@ -10173,7 +9613,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="499" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A499" s="6" t="s">
         <v>613</v>
       </c>
@@ -10184,7 +9624,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="500" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A500" s="6" t="s">
         <v>614</v>
       </c>
@@ -10195,7 +9635,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="501" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A501" s="6" t="s">
         <v>615</v>
       </c>
@@ -10206,7 +9646,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="502" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A502" s="6" t="s">
         <v>616</v>
       </c>
@@ -10217,7 +9657,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="503" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="503" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A503" s="6" t="s">
         <v>617</v>
       </c>
@@ -10228,7 +9668,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="504" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="504" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A504" s="6" t="s">
         <v>618</v>
       </c>
@@ -10239,7 +9679,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="505" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A505" s="6" t="s">
         <v>619</v>
       </c>
@@ -10250,7 +9690,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="506" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="506" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A506" s="6" t="s">
         <v>620</v>
       </c>
@@ -10261,7 +9701,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="507" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="507" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A507" s="6" t="s">
         <v>621</v>
       </c>
@@ -10272,7 +9712,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="508" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="508" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A508" s="6" t="s">
         <v>622</v>
       </c>
@@ -10283,7 +9723,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="509" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A509" s="6" t="s">
         <v>623</v>
       </c>
@@ -10294,7 +9734,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="510" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A510" s="6" t="s">
         <v>624</v>
       </c>
@@ -10305,7 +9745,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="511" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A511" s="6" t="s">
         <v>625</v>
       </c>
@@ -10316,7 +9756,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="512" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A512" s="6" t="s">
         <v>626</v>
       </c>
@@ -10327,7 +9767,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="513" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="513" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A513" s="6" t="s">
         <v>627</v>
       </c>
@@ -10338,7 +9778,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="514" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A514" s="6" t="s">
         <v>628</v>
       </c>
@@ -10349,7 +9789,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="515" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="515" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A515" s="6" t="s">
         <v>629</v>
       </c>
@@ -10360,7 +9800,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="516" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A516" s="6" t="s">
         <v>630</v>
       </c>
@@ -10371,7 +9811,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="517" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="517" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A517" s="6" t="s">
         <v>631</v>
       </c>
@@ -10382,7 +9822,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="518" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="518" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A518" s="6" t="s">
         <v>632</v>
       </c>
@@ -10393,7 +9833,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="519" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="519" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A519" s="6" t="s">
         <v>633</v>
       </c>
@@ -10404,7 +9844,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="520" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A520" s="6" t="s">
         <v>634</v>
       </c>
@@ -10415,7 +9855,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="521" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A521" s="6" t="s">
         <v>635</v>
       </c>
@@ -10426,7 +9866,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="522" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A522" s="6" t="s">
         <v>636</v>
       </c>
@@ -10437,7 +9877,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="523" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A523" s="6" t="s">
         <v>637</v>
       </c>
@@ -10448,7 +9888,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="524" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A524" s="6" t="s">
         <v>638</v>
       </c>
@@ -10459,7 +9899,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="525" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="525" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A525" s="6" t="s">
         <v>639</v>
       </c>
@@ -10470,7 +9910,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="526" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="526" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A526" s="6" t="s">
         <v>640</v>
       </c>
@@ -10481,7 +9921,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="527" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="527" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A527" s="6" t="s">
         <v>641</v>
       </c>
@@ -10492,7 +9932,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="528" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A528" s="6" t="s">
         <v>642</v>
       </c>
@@ -10503,7 +9943,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="529" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A529" s="6" t="s">
         <v>643</v>
       </c>
@@ -10514,7 +9954,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="530" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A530" s="6" t="s">
         <v>644</v>
       </c>
@@ -10525,7 +9965,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="531" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A531" s="6" t="s">
         <v>645</v>
       </c>
@@ -10536,7 +9976,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="532" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A532" s="6" t="s">
         <v>646</v>
       </c>
@@ -10547,7 +9987,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="533" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A533" s="6" t="s">
         <v>647</v>
       </c>
@@ -10558,7 +9998,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="534" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="534" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A534" s="6" t="s">
         <v>648</v>
       </c>
@@ -10569,7 +10009,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="535" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A535" s="6" t="s">
         <v>649</v>
       </c>
@@ -10580,7 +10020,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="536" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A536" s="6" t="s">
         <v>650</v>
       </c>
@@ -10591,7 +10031,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="537" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A537" s="6" t="s">
         <v>651</v>
       </c>
@@ -10602,7 +10042,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="538" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A538" s="6" t="s">
         <v>652</v>
       </c>
@@ -10613,7 +10053,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="539" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A539" s="6" t="s">
         <v>653</v>
       </c>
@@ -10624,7 +10064,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="540" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A540" s="6" t="s">
         <v>654</v>
       </c>
@@ -10635,7 +10075,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="541" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A541" s="6" t="s">
         <v>655</v>
       </c>
@@ -10646,7 +10086,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="542" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A542" s="6" t="s">
         <v>656</v>
       </c>
@@ -10657,7 +10097,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="543" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="543" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A543" s="6" t="s">
         <v>657</v>
       </c>
@@ -10668,7 +10108,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="544" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A544" s="6" t="s">
         <v>658</v>
       </c>
@@ -10679,7 +10119,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="545" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A545" s="6" t="s">
         <v>659</v>
       </c>
@@ -10690,7 +10130,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="546" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A546" s="6" t="s">
         <v>660</v>
       </c>
@@ -10701,7 +10141,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="547" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A547" s="6" t="s">
         <v>661</v>
       </c>
@@ -10712,7 +10152,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="548" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A548" s="6" t="s">
         <v>662</v>
       </c>
@@ -10723,7 +10163,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="549" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A549" s="6" t="s">
         <v>663</v>
       </c>
@@ -10734,7 +10174,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="550" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A550" s="6" t="s">
         <v>664</v>
       </c>
@@ -10745,7 +10185,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="551" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A551" s="6" t="s">
         <v>665</v>
       </c>
@@ -10756,7 +10196,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="552" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A552" s="6" t="s">
         <v>666</v>
       </c>
@@ -10767,7 +10207,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="553" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A553" s="6" t="s">
         <v>667</v>
       </c>
@@ -10778,7 +10218,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="554" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A554" s="6" t="s">
         <v>668</v>
       </c>
@@ -10789,7 +10229,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="555" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A555" s="6" t="s">
         <v>669</v>
       </c>
@@ -10800,7 +10240,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="556" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="556" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A556" s="6" t="s">
         <v>670</v>
       </c>
@@ -10811,7 +10251,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="557" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A557" s="6" t="s">
         <v>671</v>
       </c>
@@ -10822,7 +10262,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="558" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="558" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A558" s="6" t="s">
         <v>672</v>
       </c>
@@ -10833,7 +10273,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="559" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="559" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A559" s="6" t="s">
         <v>673</v>
       </c>
@@ -10844,7 +10284,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="560" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A560" s="6" t="s">
         <v>674</v>
       </c>
@@ -10855,7 +10295,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="561" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A561" s="6" t="s">
         <v>675</v>
       </c>
@@ -10866,7 +10306,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="562" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A562" s="6" t="s">
         <v>676</v>
       </c>
@@ -10877,7 +10317,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="563" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A563" s="6" t="s">
         <v>677</v>
       </c>
@@ -10888,7 +10328,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="564" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A564" s="6" t="s">
         <v>678</v>
       </c>
@@ -10899,7 +10339,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="565" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A565" s="6" t="s">
         <v>679</v>
       </c>
@@ -10910,7 +10350,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="566" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A566" s="6" t="s">
         <v>680</v>
       </c>
@@ -10921,7 +10361,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="567" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A567" s="6" t="s">
         <v>681</v>
       </c>
@@ -10932,7 +10372,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="568" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A568" s="6" t="s">
         <v>682</v>
       </c>
@@ -10943,7 +10383,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="569" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A569" s="6" t="s">
         <v>683</v>
       </c>
@@ -10954,7 +10394,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="570" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A570" s="6" t="s">
         <v>684</v>
       </c>
@@ -10965,7 +10405,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="571" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A571" s="6" t="s">
         <v>685</v>
       </c>
@@ -10976,7 +10416,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="572" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A572" s="6" t="s">
         <v>686</v>
       </c>
@@ -10987,7 +10427,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="573" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A573" s="6" t="s">
         <v>687</v>
       </c>
@@ -10998,7 +10438,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="574" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A574" s="6" t="s">
         <v>688</v>
       </c>
@@ -11009,7 +10449,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="575" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A575" s="6" t="s">
         <v>689</v>
       </c>
@@ -11020,7 +10460,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="576" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A576" s="6" t="s">
         <v>690</v>
       </c>
@@ -11031,7 +10471,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="577" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A577" s="6" t="s">
         <v>691</v>
       </c>
@@ -11042,7 +10482,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="578" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A578" s="6" t="s">
         <v>692</v>
       </c>
@@ -11053,7 +10493,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="579" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A579" s="6" t="s">
         <v>693</v>
       </c>
@@ -11064,7 +10504,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="580" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A580" s="6" t="s">
         <v>694</v>
       </c>
@@ -11075,7 +10515,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="581" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A581" s="6" t="s">
         <v>695</v>
       </c>
@@ -11086,7 +10526,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="582" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A582" s="6" t="s">
         <v>696</v>
       </c>
@@ -11097,7 +10537,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="583" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A583" s="6" t="s">
         <v>697</v>
       </c>
@@ -11108,7 +10548,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="584" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A584" s="6" t="s">
         <v>698</v>
       </c>
@@ -11119,7 +10559,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="585" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="585" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A585" s="6" t="s">
         <v>699</v>
       </c>
@@ -11130,7 +10570,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="586" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A586" s="6" t="s">
         <v>700</v>
       </c>
@@ -11141,7 +10581,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="587" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A587" s="6" t="s">
         <v>701</v>
       </c>
@@ -11152,7 +10592,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="588" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A588" s="6" t="s">
         <v>702</v>
       </c>
@@ -11163,7 +10603,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="589" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A589" s="6" t="s">
         <v>703</v>
       </c>
@@ -11174,7 +10614,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="590" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="590" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A590" s="6" t="s">
         <v>704</v>
       </c>
@@ -11185,7 +10625,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="591" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A591" s="6" t="s">
         <v>705</v>
       </c>
@@ -11196,7 +10636,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="592" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="592" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A592" s="6" t="s">
         <v>706</v>
       </c>
@@ -11207,7 +10647,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="593" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="593" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A593" s="6" t="s">
         <v>707</v>
       </c>
@@ -11218,7 +10658,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="594" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A594" s="6" t="s">
         <v>708</v>
       </c>
@@ -11229,7 +10669,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="595" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="595" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A595" s="6" t="s">
         <v>709</v>
       </c>
@@ -11240,7 +10680,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="596" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="596" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A596" s="6" t="s">
         <v>710</v>
       </c>
@@ -11251,7 +10691,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="597" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="597" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A597" s="6" t="s">
         <v>711</v>
       </c>
@@ -11262,7 +10702,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="598" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="598" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A598" s="6" t="s">
         <v>712</v>
       </c>
@@ -11273,7 +10713,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="599" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="599" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A599" s="6" t="s">
         <v>713</v>
       </c>
@@ -11284,7 +10724,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="600" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="600" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A600" s="6" t="s">
         <v>714</v>
       </c>
@@ -11295,7 +10735,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="601" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="601" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A601" s="6" t="s">
         <v>715</v>
       </c>
@@ -11306,7 +10746,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="602" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="602" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A602" s="6" t="s">
         <v>716</v>
       </c>
@@ -11317,7 +10757,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="603" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="603" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A603" s="6" t="s">
         <v>717</v>
       </c>
@@ -11328,7 +10768,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="604" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="604" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A604" s="6" t="s">
         <v>718</v>
       </c>
@@ -11339,7 +10779,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="605" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="605" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A605" s="6" t="s">
         <v>719</v>
       </c>
@@ -11350,7 +10790,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="606" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="606" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A606" s="6" t="s">
         <v>720</v>
       </c>
@@ -11361,7 +10801,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="607" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A607" s="6" t="s">
         <v>721</v>
       </c>
@@ -11372,7 +10812,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="608" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A608" s="6" t="s">
         <v>722</v>
       </c>
@@ -11383,7 +10823,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="609" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="609" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A609" s="6" t="s">
         <v>723</v>
       </c>
@@ -11394,7 +10834,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="610" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="610" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A610" s="6" t="s">
         <v>724</v>
       </c>
@@ -11405,7 +10845,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="611" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="611" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A611" s="6" t="s">
         <v>725</v>
       </c>
@@ -11416,7 +10856,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="612" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="612" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A612" s="6" t="s">
         <v>726</v>
       </c>
@@ -11427,7 +10867,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="613" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="613" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A613" s="6" t="s">
         <v>727</v>
       </c>
@@ -11438,7 +10878,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="614" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="614" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A614" s="6" t="s">
         <v>728</v>
       </c>
@@ -11449,7 +10889,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="615" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="615" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A615" s="6" t="s">
         <v>729</v>
       </c>
@@ -11460,7 +10900,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="616" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="616" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A616" s="6" t="s">
         <v>730</v>
       </c>
@@ -11471,7 +10911,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="617" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="617" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A617" s="6" t="s">
         <v>731</v>
       </c>
@@ -11482,7 +10922,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="618" spans="1:3" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="618" ht="15.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A618" s="6" t="s">
         <v>732</v>
       </c>
@@ -11495,6 +10935,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/data/Markspen_Engineering_Central_Monitor.xlsx
+++ b/data/Markspen_Engineering_Central_Monitor.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1513" uniqueCount="798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1517" uniqueCount="799">
   <si>
     <t>Branch</t>
   </si>
@@ -2311,6 +2311,9 @@
   </si>
   <si>
     <t>Lead Technician</t>
+  </si>
+  <si>
+    <t>Yes</t>
   </si>
   <si>
     <t>Visit Id</t>
@@ -3086,7 +3089,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="8.85546875"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
@@ -3105,6 +3108,20 @@
       </c>
       <c r="D1" s="10" t="s">
         <v>760</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>753</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" t="s">
+        <v>761</v>
       </c>
     </row>
   </sheetData>
@@ -3134,7 +3151,7 @@
   <sheetData>
     <row r="1" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>733</v>
@@ -3146,25 +3163,25 @@
         <v>37</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="L1" s="10" t="s">
         <v>81</v>
@@ -3176,7 +3193,7 @@
         <v>106</v>
       </c>
       <c r="O1" s="10" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
   </sheetData>
@@ -3208,25 +3225,25 @@
         <v>115</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
   </sheetData>
@@ -3255,43 +3272,43 @@
   <sheetData>
     <row r="1" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>733</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="F1" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="L1" s="10" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="M1" s="10" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
   </sheetData>
@@ -3328,37 +3345,37 @@
         <v>0</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="L1" s="10" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="M1" s="10" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="N1" s="10" t="s">
         <v>27</v>
@@ -3367,7 +3384,7 @@
         <v>752</v>
       </c>
       <c r="P1" s="10" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
   </sheetData>
